--- a/excel/Pharmacy_OLAP_Operations.xlsx
+++ b/excel/Pharmacy_OLAP_Operations.xlsx
@@ -1,24 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SLIIT Y3S1\DWBI assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54C59DE1-00F4-4E36-BEDA-86D5AF9DE2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3169416-E5D0-479A-80F9-F3B16392315B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3EEAC5A7-0A19-4F0E-BB35-17D123B52D9B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3EEAC5A7-0A19-4F0E-BB35-17D123B52D9B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="pivot" sheetId="2" r:id="rId1"/>
+    <sheet name="dril down" sheetId="1" r:id="rId2"/>
+    <sheet name="slice" sheetId="5" r:id="rId3"/>
+    <sheet name="rollup" sheetId="3" r:id="rId4"/>
+    <sheet name="dice" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="79" r:id="rId3"/>
+    <pivotCache cacheId="6" r:id="rId6"/>
+    <pivotCache cacheId="52" r:id="rId7"/>
+    <pivotCache cacheId="88" r:id="rId8"/>
+    <pivotCache cacheId="134" r:id="rId9"/>
+    <pivotCache cacheId="137" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,15 +48,76 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{17022451-237A-46F1-BEAA-6B8D53A83938}" odcFile="C:\Users\ASUS\OneDrive\Documents\My Data Sources\localhost_MSSQLSERVER2 Phamacy_cube Pharmacy DW.odc" keepAlive="1" name="localhost_MSSQLSERVER2 Phamacy_cube Pharmacy DW" type="5" refreshedVersion="8" background="1">
+  <connection id="1" xr16:uid="{A4577DD8-25BA-4BB2-839C-44FD6814A8B8}" odcFile="C:\Users\ASUS\OneDrive\Documents\My Data Sources\DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW.odc" keepAlive="1" name="DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW" type="5" refreshedVersion="8" background="1">
+    <dbPr connection="Provider=MSOLAP.8;Integrated Security=SSPI;Persist Security Info=True;Initial Catalog=Phamacy_cube;Data Source=DESKTOP-LS0G58P\MSSQLSERVER2;MDX Compatibility=1;Safety Options=2;MDX Missing Member Mode=Error;Update Isolation Level=2" command="Pharmacy DW" commandType="1"/>
+    <olapPr sendLocale="1" rowDrillCount="1000"/>
+  </connection>
+  <connection id="2" xr16:uid="{B1B3BD4F-F06F-4BB7-B62E-F30B5C17294B}" odcFile="C:\Users\ASUS\OneDrive\Documents\My Data Sources\DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW.odc" keepAlive="1" name="DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW1" type="5" refreshedVersion="8" background="1">
+    <dbPr connection="Provider=MSOLAP.8;Integrated Security=SSPI;Persist Security Info=True;Initial Catalog=Phamacy_cube;Data Source=DESKTOP-LS0G58P\MSSQLSERVER2;MDX Compatibility=1;Safety Options=2;MDX Missing Member Mode=Error;Update Isolation Level=2" command="Pharmacy DW" commandType="1"/>
+    <olapPr sendLocale="1" rowDrillCount="1000"/>
+  </connection>
+  <connection id="3" xr16:uid="{DAECB603-1EE3-4780-90B6-3FBA08EF36E8}" odcFile="C:\Users\ASUS\OneDrive\Documents\My Data Sources\DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW.odc" keepAlive="1" name="DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW2" type="5" refreshedVersion="8" background="1">
+    <dbPr connection="Provider=MSOLAP.8;Integrated Security=SSPI;Persist Security Info=True;Initial Catalog=Phamacy_cube;Data Source=DESKTOP-LS0G58P\MSSQLSERVER2;MDX Compatibility=1;Safety Options=2;MDX Missing Member Mode=Error;Update Isolation Level=2" command="Pharmacy DW" commandType="1"/>
+    <olapPr sendLocale="1" rowDrillCount="1000"/>
+  </connection>
+  <connection id="4" xr16:uid="{1B753D25-0F29-441E-8C29-BF4FB5A9A6F0}" odcFile="C:\Users\ASUS\OneDrive\Documents\My Data Sources\DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW.odc" keepAlive="1" name="DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW3" type="5" refreshedVersion="8" background="1">
+    <dbPr connection="Provider=MSOLAP.8;Integrated Security=SSPI;Persist Security Info=True;Initial Catalog=Phamacy_cube;Data Source=DESKTOP-LS0G58P\MSSQLSERVER2;MDX Compatibility=1;Safety Options=2;MDX Missing Member Mode=Error;Update Isolation Level=2" command="Pharmacy DW" commandType="1"/>
+    <olapPr sendLocale="1" rowDrillCount="1000"/>
+  </connection>
+  <connection id="5" xr16:uid="{AAB98C6A-2969-432F-A521-FED37175FE24}" odcFile="C:\Users\ASUS\OneDrive\Documents\My Data Sources\DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW.odc" keepAlive="1" name="DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW4" type="5" refreshedVersion="8" background="1">
+    <dbPr connection="Provider=MSOLAP.8;Integrated Security=SSPI;Persist Security Info=True;Initial Catalog=Phamacy_cube;Data Source=DESKTOP-LS0G58P\MSSQLSERVER2;MDX Compatibility=1;Safety Options=2;MDX Missing Member Mode=Error;Update Isolation Level=2" command="Pharmacy DW" commandType="1"/>
+    <olapPr sendLocale="1" rowDrillCount="1000"/>
+  </connection>
+  <connection id="6" xr16:uid="{4494F3AB-6367-4B4F-AEED-38358A6A0AF5}" odcFile="C:\Users\ASUS\OneDrive\Documents\My Data Sources\DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW.odc" keepAlive="1" name="DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW5" type="5" refreshedVersion="8" background="1">
+    <dbPr connection="Provider=MSOLAP.8;Integrated Security=SSPI;Persist Security Info=True;Initial Catalog=Phamacy_cube;Data Source=DESKTOP-LS0G58P\MSSQLSERVER2;MDX Compatibility=1;Safety Options=2;MDX Missing Member Mode=Error;Update Isolation Level=2" command="Pharmacy DW" commandType="1"/>
+    <olapPr sendLocale="1" rowDrillCount="1000"/>
+  </connection>
+  <connection id="7" xr16:uid="{17022451-237A-46F1-BEAA-6B8D53A83938}" odcFile="C:\Users\ASUS\OneDrive\Documents\My Data Sources\localhost_MSSQLSERVER2 Phamacy_cube Pharmacy DW.odc" keepAlive="1" name="localhost_MSSQLSERVER2 Phamacy_cube Pharmacy DW" type="5" refreshedVersion="8" background="1">
     <dbPr connection="Provider=MSOLAP.8;Integrated Security=SSPI;Persist Security Info=True;Initial Catalog=Phamacy_cube;Data Source=localhost\MSSQLSERVER2;MDX Compatibility=1;Safety Options=2;MDX Missing Member Mode=Error;Update Isolation Level=2" command="Pharmacy DW" commandType="1"/>
     <olapPr sendLocale="1" rowDrillCount="1000"/>
   </connection>
 </connections>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <metadataTypes count="1">
+    <metadataType name="XLMDX" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <metadataStrings count="5">
+    <s v="DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW3"/>
+    <s v="{[Dim Product].[Category].[All]}"/>
+    <s v="DESKTOP-LS0G58P_MSSQLSERVER2 Phamacy_cube Pharmacy DW5"/>
+    <s v="{[Dim Product].[Category].&amp;[Antibiotics &amp; Anti-infectives]}"/>
+    <s v="{[Dim Product].[Subcategory].&amp;[Drops]}"/>
+  </metadataStrings>
+  <mdxMetadata count="3">
+    <mdx n="0" f="s">
+      <ms ns="1" c="0"/>
+    </mdx>
+    <mdx n="2" f="s">
+      <ms ns="3" c="0"/>
+    </mdx>
+    <mdx n="2" f="s">
+      <ms ns="4" c="0"/>
+    </mdx>
+  </mdxMetadata>
+  <valueMetadata count="3">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="22">
   <si>
     <t>Gross Amount</t>
   </si>
@@ -98,6 +166,24 @@
   <si>
     <t>Column Labels</t>
   </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Subcategory</t>
+  </si>
+  <si>
+    <t>Antibiotics &amp; Anti-infectives</t>
+  </si>
+  <si>
+    <t>Drops</t>
+  </si>
 </sst>
 </file>
 
@@ -132,12 +218,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -156,9 +248,1003 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Pharmacy_OLAP_Operations.xlsx]dril down!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'dril down'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'dril down'!$A$2:$A$7</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="4"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>4</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2015</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'dril down'!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2909823288.3499908</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3712346352.1499872</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4217305361.4300017</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4412908786.2599974</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-35B2-4C3D-9A50-568FFB0A5416}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1415957599"/>
+        <c:axId val="1415958079"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1415957599"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1415958079"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1415958079"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1415957599"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F0A174F-467E-5837-94CB-4CF8FD7AB3DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Senan Jayasinghe" refreshedDate="46113.921238657407" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{0F8130A0-49C5-4D58-8234-B3D92C2B77FE}">
-  <cacheSource type="external" connectionId="1"/>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Senan Jayasinghe" refreshedDate="46139.936796527778" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{0F8130A0-49C5-4D58-8234-B3D92C2B77FE}">
+  <cacheSource type="external" connectionId="7"/>
   <cacheFields count="5">
     <cacheField name="[Measures].[Gross Amount]" caption="Gross Amount" numFmtId="0" hierarchy="10" level="32767"/>
     <cacheField name="[Dim Date].[Quarter Number].[Quarter Number]" caption="Quarter Number" numFmtId="0" hierarchy="5" level="1" mappingCount="1">
@@ -257,8 +1343,428 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Senan Jayasinghe" refreshedDate="46139.964796296299" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{0D67C554-2B61-46C9-8077-7C51BC9A3999}">
+  <cacheSource type="external" connectionId="3"/>
+  <cacheFields count="8">
+    <cacheField name="[Dim Date].[Hierarchy].[Year Number]" caption="Year Number" numFmtId="0" hierarchy="3" level="1">
+      <sharedItems count="1">
+        <s v="[Dim Date].[Hierarchy].[Year Number].&amp;[2015]" c="2015"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Quarter Number]" caption="Quarter Number" numFmtId="0" hierarchy="3" level="2" mappingCount="1">
+      <sharedItems count="4">
+        <s v="[Dim Date].[Hierarchy].[Quarter Number].&amp;[1]" c="1"/>
+        <s v="[Dim Date].[Hierarchy].[Quarter Number].&amp;[2]" c="2"/>
+        <s v="[Dim Date].[Hierarchy].[Quarter Number].&amp;[3]" c="3"/>
+        <s v="[Dim Date].[Hierarchy].[Quarter Number].&amp;[4]" c="4"/>
+      </sharedItems>
+      <mpMap v="4"/>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Month Number]" caption="Month Number" numFmtId="0" hierarchy="3" level="3" mappingCount="1">
+      <sharedItems count="3">
+        <s v="[Dim Date].[Hierarchy].[Month Number].&amp;[1]" c="1"/>
+        <s v="[Dim Date].[Hierarchy].[Month Number].&amp;[2]" c="2"/>
+        <s v="[Dim Date].[Hierarchy].[Month Number].&amp;[3]" c="3"/>
+      </sharedItems>
+      <mpMap v="5"/>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Full Date]" caption="Full Date" numFmtId="0" hierarchy="3" level="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Quarter Number].[Year Number]" caption="Year Number" propertyName="Year Number" numFmtId="0" hierarchy="3" level="2" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2015" maxValue="2015" count="1">
+        <n v="2015"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Month Number].[Quarter Number]" caption="Quarter Number" propertyName="Quarter Number" numFmtId="0" hierarchy="3" level="3" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1" count="1">
+        <n v="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Full Date].[Month Number]" caption="Month Number" propertyName="Month Number" numFmtId="0" hierarchy="3" level="4" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Measures].[Gross Amount]" caption="Gross Amount" numFmtId="0" hierarchy="10" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="15">
+    <cacheHierarchy uniqueName="[Dim Customer].[Customer Key]" caption="Customer Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Customer].[Customer Key].[All]" allUniqueName="[Dim Customer].[Customer Key].[All]" dimensionUniqueName="[Dim Customer]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Date].[Date Key].[All]" allUniqueName="[Dim Date].[Date Key].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Date].[Full Date].[All]" allUniqueName="[Dim Date].[Full Date].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Hierarchy]" caption="Hierarchy" defaultMemberUniqueName="[Dim Date].[Hierarchy].[All]" allUniqueName="[Dim Date].[Hierarchy].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="5" unbalanced="0">
+      <fieldsUsage count="5">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+        <fieldUsage x="1"/>
+        <fieldUsage x="2"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Date].[Month Number]" caption="Month Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Month Number].[All]" allUniqueName="[Dim Date].[Month Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Quarter Number]" caption="Quarter Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Quarter Number].[All]" allUniqueName="[Dim Date].[Quarter Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Year Number]" caption="Year Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Year Number].[All]" allUniqueName="[Dim Date].[Year Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Doctor].[Doctor Key]" caption="Doctor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Doctor].[Doctor Key].[All]" allUniqueName="[Dim Doctor].[Doctor Key].[All]" dimensionUniqueName="[Dim Doctor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Product].[Product Key]" caption="Product Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Product].[Product Key].[All]" allUniqueName="[Dim Product].[Product Key].[All]" dimensionUniqueName="[Dim Product]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Quantity]" caption="Quantity" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Gross Amount]" caption="Gross Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="7"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Cost Amount]" caption="Cost Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Profit Amount]" caption="Profit Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Txn Process Time Hours]" caption="Txn Process Time Hours" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Sales Count]" caption="Fact Sales Count" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="5">
+    <dimension name="Dim Customer" uniqueName="[Dim Customer]" caption="Dim Customer"/>
+    <dimension name="Dim Date" uniqueName="[Dim Date]" caption="Dim Date"/>
+    <dimension name="Dim Doctor" uniqueName="[Dim Doctor]" caption="Dim Doctor"/>
+    <dimension name="Dim Product" uniqueName="[Dim Product]" caption="Dim Product"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Sales" caption="Fact Sales"/>
+  </measureGroups>
+  <maps count="4">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Senan Jayasinghe" refreshedDate="46139.973870717593" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{56E532D4-D452-4E60-B4BF-FCD7E98E7CC2}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="8">
+    <cacheField name="[Dim Date].[Hierarchy].[Year Number]" caption="Year Number" numFmtId="0" hierarchy="3" level="1">
+      <sharedItems count="1">
+        <s v="[Dim Date].[Hierarchy].[Year Number].&amp;[2015]" c="2015"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Quarter Number]" caption="Quarter Number" numFmtId="0" hierarchy="3" level="2" mappingCount="1">
+      <sharedItems count="4">
+        <s v="[Dim Date].[Hierarchy].[Quarter Number].&amp;[1]" c="1"/>
+        <s v="[Dim Date].[Hierarchy].[Quarter Number].&amp;[2]" c="2"/>
+        <s v="[Dim Date].[Hierarchy].[Quarter Number].&amp;[3]" c="3"/>
+        <s v="[Dim Date].[Hierarchy].[Quarter Number].&amp;[4]" c="4"/>
+      </sharedItems>
+      <mpMap v="4"/>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Month Number]" caption="Month Number" numFmtId="0" hierarchy="3" level="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Full Date]" caption="Full Date" numFmtId="0" hierarchy="3" level="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Quarter Number].[Year Number]" caption="Year Number" propertyName="Year Number" numFmtId="0" hierarchy="3" level="2" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2015" maxValue="2015" count="1">
+        <n v="2015"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Month Number].[Quarter Number]" caption="Quarter Number" propertyName="Quarter Number" numFmtId="0" hierarchy="3" level="3" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Date].[Hierarchy].[Full Date].[Month Number]" caption="Month Number" propertyName="Month Number" numFmtId="0" hierarchy="3" level="4" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Measures].[Gross Amount]" caption="Gross Amount" numFmtId="0" hierarchy="10" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="15">
+    <cacheHierarchy uniqueName="[Dim Customer].[Customer Key]" caption="Customer Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Customer].[Customer Key].[All]" allUniqueName="[Dim Customer].[Customer Key].[All]" dimensionUniqueName="[Dim Customer]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Date].[Date Key].[All]" allUniqueName="[Dim Date].[Date Key].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Date].[Full Date].[All]" allUniqueName="[Dim Date].[Full Date].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Hierarchy]" caption="Hierarchy" defaultMemberUniqueName="[Dim Date].[Hierarchy].[All]" allUniqueName="[Dim Date].[Hierarchy].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="5" unbalanced="0">
+      <fieldsUsage count="5">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+        <fieldUsage x="1"/>
+        <fieldUsage x="2"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Date].[Month Number]" caption="Month Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Month Number].[All]" allUniqueName="[Dim Date].[Month Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Quarter Number]" caption="Quarter Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Quarter Number].[All]" allUniqueName="[Dim Date].[Quarter Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Year Number]" caption="Year Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Year Number].[All]" allUniqueName="[Dim Date].[Year Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Doctor].[Doctor Key]" caption="Doctor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Doctor].[Doctor Key].[All]" allUniqueName="[Dim Doctor].[Doctor Key].[All]" dimensionUniqueName="[Dim Doctor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Product].[Product Key]" caption="Product Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Product].[Product Key].[All]" allUniqueName="[Dim Product].[Product Key].[All]" dimensionUniqueName="[Dim Product]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Quantity]" caption="Quantity" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Gross Amount]" caption="Gross Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="7"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Cost Amount]" caption="Cost Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Profit Amount]" caption="Profit Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Txn Process Time Hours]" caption="Txn Process Time Hours" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Sales Count]" caption="Fact Sales Count" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="5">
+    <dimension name="Dim Customer" uniqueName="[Dim Customer]" caption="Dim Customer"/>
+    <dimension name="Dim Date" uniqueName="[Dim Date]" caption="Dim Date"/>
+    <dimension name="Dim Doctor" uniqueName="[Dim Doctor]" caption="Dim Doctor"/>
+    <dimension name="Dim Product" uniqueName="[Dim Product]" caption="Dim Product"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Sales" caption="Fact Sales"/>
+  </measureGroups>
+  <maps count="4">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Senan Jayasinghe" refreshedDate="46139.983145254628" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9274F2EB-9386-4FB3-9076-A47B9E62E2F9}">
+  <cacheSource type="external" connectionId="6"/>
+  <cacheFields count="7">
+    <cacheField name="[Measures].[Gross Amount]" caption="Gross Amount" numFmtId="0" hierarchy="13" level="32767"/>
+    <cacheField name="[Dim Date].[Quarter Number].[Quarter Number]" caption="Quarter Number" numFmtId="0" hierarchy="5" level="1" mappingCount="1">
+      <sharedItems count="4">
+        <s v="[Dim Date].[Quarter Number].&amp;[1]" c="1"/>
+        <s v="[Dim Date].[Quarter Number].&amp;[2]" c="2"/>
+        <s v="[Dim Date].[Quarter Number].&amp;[3]" c="3"/>
+        <s v="[Dim Date].[Quarter Number].&amp;[4]" c="4"/>
+      </sharedItems>
+      <mpMap v="2"/>
+    </cacheField>
+    <cacheField name="[Dim Date].[Quarter Number].[Quarter Number].[Year Number]" caption="Year Number" propertyName="Year Number" numFmtId="0" hierarchy="5" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2015" maxValue="2015" count="1">
+        <n v="2015"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Date].[Month Number].[Month Number]" caption="Month Number" numFmtId="0" hierarchy="4" level="1" mappingCount="1">
+      <sharedItems count="11">
+        <s v="[Dim Date].[Month Number].&amp;[1]" c="1"/>
+        <s v="[Dim Date].[Month Number].&amp;[10]" c="10"/>
+        <s v="[Dim Date].[Month Number].&amp;[12]" c="12"/>
+        <s v="[Dim Date].[Month Number].&amp;[2]" c="2"/>
+        <s v="[Dim Date].[Month Number].&amp;[3]" c="3"/>
+        <s v="[Dim Date].[Month Number].&amp;[4]" c="4"/>
+        <s v="[Dim Date].[Month Number].&amp;[5]" c="5"/>
+        <s v="[Dim Date].[Month Number].&amp;[6]" c="6"/>
+        <s v="[Dim Date].[Month Number].&amp;[7]" c="7"/>
+        <s v="[Dim Date].[Month Number].&amp;[8]" c="8"/>
+        <s v="[Dim Date].[Month Number].&amp;[9]" c="9"/>
+      </sharedItems>
+      <mpMap v="4"/>
+    </cacheField>
+    <cacheField name="[Dim Date].[Month Number].[Month Number].[Quarter Number]" caption="Quarter Number" propertyName="Quarter Number" numFmtId="0" hierarchy="4" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="4" count="4">
+        <n v="1"/>
+        <n v="4"/>
+        <n v="2"/>
+        <n v="3"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Product].[Category].[Category]" caption="Category" numFmtId="0" hierarchy="8" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Product].[Subcategory].[Subcategory]" caption="Subcategory" numFmtId="0" hierarchy="11" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="18">
+    <cacheHierarchy uniqueName="[Dim Customer].[Customer Key]" caption="Customer Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Customer].[Customer Key].[All]" allUniqueName="[Dim Customer].[Customer Key].[All]" dimensionUniqueName="[Dim Customer]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Date].[Date Key].[All]" allUniqueName="[Dim Date].[Date Key].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Date].[Full Date].[All]" allUniqueName="[Dim Date].[Full Date].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Hierarchy]" caption="Hierarchy" defaultMemberUniqueName="[Dim Date].[Hierarchy].[All]" allUniqueName="[Dim Date].[Hierarchy].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Month Number]" caption="Month Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Month Number].[All]" allUniqueName="[Dim Date].[Month Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Date].[Quarter Number]" caption="Quarter Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Quarter Number].[All]" allUniqueName="[Dim Date].[Quarter Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Date].[Year Number]" caption="Year Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Year Number].[All]" allUniqueName="[Dim Date].[Year Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Doctor].[Doctor Key]" caption="Doctor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Doctor].[Doctor Key].[All]" allUniqueName="[Dim Doctor].[Doctor Key].[All]" dimensionUniqueName="[Dim Doctor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Product].[Category]" caption="Category" attribute="1" defaultMemberUniqueName="[Dim Product].[Category].[All]" allUniqueName="[Dim Product].[Category].[All]" dimensionUniqueName="[Dim Product]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Product].[Product Key]" caption="Product Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Product].[Product Key].[All]" allUniqueName="[Dim Product].[Product Key].[All]" dimensionUniqueName="[Dim Product]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Product].[Product Name]" caption="Product Name" attribute="1" defaultMemberUniqueName="[Dim Product].[Product Name].[All]" allUniqueName="[Dim Product].[Product Name].[All]" dimensionUniqueName="[Dim Product]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Product].[Subcategory]" caption="Subcategory" attribute="1" defaultMemberUniqueName="[Dim Product].[Subcategory].[All]" allUniqueName="[Dim Product].[Subcategory].[All]" dimensionUniqueName="[Dim Product]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Quantity]" caption="Quantity" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Gross Amount]" caption="Gross Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Cost Amount]" caption="Cost Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Profit Amount]" caption="Profit Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Txn Process Time Hours]" caption="Txn Process Time Hours" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Sales Count]" caption="Fact Sales Count" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="5">
+    <dimension name="Dim Customer" uniqueName="[Dim Customer]" caption="Dim Customer"/>
+    <dimension name="Dim Date" uniqueName="[Dim Date]" caption="Dim Date"/>
+    <dimension name="Dim Doctor" uniqueName="[Dim Doctor]" caption="Dim Doctor"/>
+    <dimension name="Dim Product" uniqueName="[Dim Product]" caption="Dim Product"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Sales" caption="Fact Sales"/>
+  </measureGroups>
+  <maps count="4">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Senan Jayasinghe" refreshedDate="46139.983601736109" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{3FF7E45B-A6FA-48F2-8B11-5D7B39527F4E}">
+  <cacheSource type="external" connectionId="4"/>
+  <cacheFields count="6">
+    <cacheField name="[Dim Date].[Quarter Number].[Quarter Number]" caption="Quarter Number" numFmtId="0" hierarchy="5" level="1" mappingCount="1">
+      <sharedItems count="4">
+        <s v="[Dim Date].[Quarter Number].&amp;[1]" c="1"/>
+        <s v="[Dim Date].[Quarter Number].&amp;[2]" c="2"/>
+        <s v="[Dim Date].[Quarter Number].&amp;[3]" c="3"/>
+        <s v="[Dim Date].[Quarter Number].&amp;[4]" c="4"/>
+      </sharedItems>
+      <mpMap v="1"/>
+    </cacheField>
+    <cacheField name="[Dim Date].[Quarter Number].[Quarter Number].[Year Number]" caption="Year Number" propertyName="Year Number" numFmtId="0" hierarchy="5" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2015" maxValue="2015" count="1">
+        <n v="2015"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Date].[Month Number].[Month Number]" caption="Month Number" numFmtId="0" hierarchy="4" level="1" mappingCount="1">
+      <sharedItems count="12">
+        <s v="[Dim Date].[Month Number].&amp;[1]" c="1"/>
+        <s v="[Dim Date].[Month Number].&amp;[10]" c="10"/>
+        <s v="[Dim Date].[Month Number].&amp;[11]" c="11"/>
+        <s v="[Dim Date].[Month Number].&amp;[12]" c="12"/>
+        <s v="[Dim Date].[Month Number].&amp;[2]" c="2"/>
+        <s v="[Dim Date].[Month Number].&amp;[3]" c="3"/>
+        <s v="[Dim Date].[Month Number].&amp;[4]" c="4"/>
+        <s v="[Dim Date].[Month Number].&amp;[5]" c="5"/>
+        <s v="[Dim Date].[Month Number].&amp;[6]" c="6"/>
+        <s v="[Dim Date].[Month Number].&amp;[7]" c="7"/>
+        <s v="[Dim Date].[Month Number].&amp;[8]" c="8"/>
+        <s v="[Dim Date].[Month Number].&amp;[9]" c="9"/>
+      </sharedItems>
+      <mpMap v="3"/>
+    </cacheField>
+    <cacheField name="[Dim Date].[Month Number].[Month Number].[Quarter Number]" caption="Quarter Number" propertyName="Quarter Number" numFmtId="0" hierarchy="4" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="4" count="4">
+        <n v="1"/>
+        <n v="4"/>
+        <n v="2"/>
+        <n v="3"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Gross Amount]" caption="Gross Amount" numFmtId="0" hierarchy="13" level="32767"/>
+    <cacheField name="[Dim Product].[Category].[Category]" caption="Category" numFmtId="0" hierarchy="8" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="18">
+    <cacheHierarchy uniqueName="[Dim Customer].[Customer Key]" caption="Customer Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Customer].[Customer Key].[All]" allUniqueName="[Dim Customer].[Customer Key].[All]" dimensionUniqueName="[Dim Customer]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Date].[Date Key].[All]" allUniqueName="[Dim Date].[Date Key].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Date].[Full Date].[All]" allUniqueName="[Dim Date].[Full Date].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Hierarchy]" caption="Hierarchy" defaultMemberUniqueName="[Dim Date].[Hierarchy].[All]" allUniqueName="[Dim Date].[Hierarchy].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Date].[Month Number]" caption="Month Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Month Number].[All]" allUniqueName="[Dim Date].[Month Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Date].[Quarter Number]" caption="Quarter Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Quarter Number].[All]" allUniqueName="[Dim Date].[Quarter Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Date].[Year Number]" caption="Year Number" attribute="1" defaultMemberUniqueName="[Dim Date].[Year Number].[All]" allUniqueName="[Dim Date].[Year Number].[All]" dimensionUniqueName="[Dim Date]" displayFolder="" count="2" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Doctor].[Doctor Key]" caption="Doctor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Doctor].[Doctor Key].[All]" allUniqueName="[Dim Doctor].[Doctor Key].[All]" dimensionUniqueName="[Dim Doctor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Product].[Category]" caption="Category" attribute="1" defaultMemberUniqueName="[Dim Product].[Category].[All]" allUniqueName="[Dim Product].[Category].[All]" dimensionUniqueName="[Dim Product]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Product].[Product Key]" caption="Product Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Product].[Product Key].[All]" allUniqueName="[Dim Product].[Product Key].[All]" dimensionUniqueName="[Dim Product]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Product].[Product Name]" caption="Product Name" attribute="1" defaultMemberUniqueName="[Dim Product].[Product Name].[All]" allUniqueName="[Dim Product].[Product Name].[All]" dimensionUniqueName="[Dim Product]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Product].[Subcategory]" caption="Subcategory" attribute="1" defaultMemberUniqueName="[Dim Product].[Subcategory].[All]" allUniqueName="[Dim Product].[Subcategory].[All]" dimensionUniqueName="[Dim Product]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Quantity]" caption="Quantity" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Gross Amount]" caption="Gross Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Cost Amount]" caption="Cost Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Profit Amount]" caption="Profit Amount" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Txn Process Time Hours]" caption="Txn Process Time Hours" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Sales Count]" caption="Fact Sales Count" measure="1" displayFolder="" measureGroup="Fact Sales" count="0"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="5">
+    <dimension name="Dim Customer" uniqueName="[Dim Customer]" caption="Dim Customer"/>
+    <dimension name="Dim Date" uniqueName="[Dim Date]" caption="Dim Date"/>
+    <dimension name="Dim Doctor" uniqueName="[Dim Doctor]" caption="Dim Doctor"/>
+    <dimension name="Dim Product" uniqueName="[Dim Product]" caption="Dim Product"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Sales" caption="Fact Sales"/>
+  </measureGroups>
+  <maps count="4">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4984AC9B-EE5C-405F-B73E-B7596C840658}" name="PivotTable1" cacheId="79" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4984AC9B-EE5C-405F-B73E-B7596C840658}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
   <location ref="A4:F18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -388,6 +1894,501 @@
   <colHierarchiesUsage count="1">
     <colHierarchyUsage hierarchyUsage="5"/>
   </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7A57957-5FA7-4691-ADD1-98991822C828}" name="PivotTable1" cacheId="88" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+  <location ref="A1:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <items count="1">
+        <item c="1" x="0" d="1"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <items count="4">
+        <item c="1" x="0"/>
+        <item c="1" x="1"/>
+        <item c="1" x="2"/>
+        <item c="1" x="3"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
+    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
+    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
+    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="15">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy>
+      <mps count="3">
+        <mp field="4"/>
+        <mp field="5"/>
+        <mp field="6"/>
+      </mps>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="3"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF9797BD-E8CE-4B1F-BFCA-4EF09B681979}" name="PivotTable6" cacheId="137" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A3:B20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+      </items>
+    </pivotField>
+    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="17">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="5" hier="8" name="[Dim Product].[Category].[All]" cap="All"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="18">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy>
+      <mps count="1">
+        <mp field="3"/>
+      </mps>
+    </pivotHierarchy>
+    <pivotHierarchy>
+      <mps count="1">
+        <mp field="1"/>
+      </mps>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="2">
+    <rowHierarchyUsage hierarchyUsage="5"/>
+    <rowHierarchyUsage hierarchyUsage="4"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CA951F01-C1DA-4F2F-8690-F75B97888716}" name="PivotTable3" cacheId="52" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A1:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <items count="1">
+        <item c="1" x="0" d="1"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <items count="4">
+        <item c="1" x="0" d="1"/>
+        <item c="1" x="1"/>
+        <item c="1" x="2"/>
+        <item c="1" x="3"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <items count="3">
+        <item c="1" x="0"/>
+        <item c="1" x="1"/>
+        <item c="1" x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
+    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
+    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
+    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="0"/>
+    <field x="1"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="15">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy>
+      <mps count="3">
+        <mp field="4"/>
+        <mp field="5"/>
+        <mp field="6"/>
+      </mps>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="3"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96E18AD1-1DA2-43EA-9DC3-3E6F4BF0503E}" name="PivotTable8" cacheId="134" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A4:B20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="7">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="11">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+      </items>
+    </pivotField>
+    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="5" hier="8" name="[Dim Product].[Category].&amp;[Antibiotics &amp; Anti-infectives]" cap="Antibiotics &amp; Anti-infectives"/>
+    <pageField fld="6" hier="11" name="[Dim Product].[Subcategory].&amp;[Drops]" cap="Drops"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField fld="0" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="18">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy>
+      <mps count="1">
+        <mp field="4"/>
+      </mps>
+    </pivotHierarchy>
+    <pivotHierarchy>
+      <mps count="1">
+        <mp field="2"/>
+      </mps>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="2">
+    <rowHierarchyUsage hierarchyUsage="5"/>
+    <rowHierarchyUsage hierarchyUsage="4"/>
+  </rowHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
@@ -723,18 +2724,23 @@
     <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B5" t="s">
@@ -754,191 +2760,191 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1">
-        <v>663044066.46999991</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1">
-        <v>663044066.46999991</v>
+      <c r="B6" s="3">
+        <v>663044066.47000504</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
+        <v>663044066.47000504</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1">
-        <v>1641003033.2400002</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1641003033.2400002</v>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3">
+        <v>1641003033.2400024</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1641003033.2400024</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1">
-        <v>1408510868.5400002</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1408510868.5400002</v>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3">
+        <v>1408510868.5399995</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1408510868.5399995</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1">
-        <v>1363394884.4799998</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1363394884.4799998</v>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
+        <v>1363394884.4799986</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1363394884.4799986</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="1">
-        <v>951745903.29999983</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1">
-        <v>951745903.29999983</v>
+      <c r="B10" s="3">
+        <v>951745903.30000448</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3">
+        <v>951745903.30000448</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="1">
-        <v>1295033318.5799999</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1">
-        <v>1295033318.5799999</v>
+      <c r="B11" s="3">
+        <v>1295033318.5800047</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3">
+        <v>1295033318.5800047</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1">
-        <v>1226789622.46</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1">
-        <v>1226789622.46</v>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3">
+        <v>1226789622.4600055</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3">
+        <v>1226789622.4600055</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1">
-        <v>1210946390.6899998</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1">
-        <v>1210946390.6899998</v>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3">
+        <v>1210946390.6900024</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3">
+        <v>1210946390.6900024</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1">
-        <v>1274610338.9999998</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1">
-        <v>1274610338.9999998</v>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3">
+        <v>1274610339.0000014</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3">
+        <v>1274610339.0000014</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1">
-        <v>1173567470.9300001</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1">
-        <v>1173567470.9300001</v>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3">
+        <v>1173567470.9300017</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3">
+        <v>1173567470.9300017</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1">
-        <v>1343111582.6100001</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1">
-        <v>1343111582.6100001</v>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3">
+        <v>1343111582.6100006</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3">
+        <v>1343111582.6100006</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
-        <v>1700626307.8900001</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1">
-        <v>1700626307.8900001</v>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3">
+        <v>1700626307.889998</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3">
+        <v>1700626307.889998</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="1">
-        <v>2909823288.3499994</v>
-      </c>
-      <c r="C18" s="1">
-        <v>3712346352.1500006</v>
-      </c>
-      <c r="D18" s="1">
-        <v>4217305361.4300008</v>
-      </c>
-      <c r="E18" s="1">
-        <v>4412908786.2600021</v>
-      </c>
-      <c r="F18" s="1">
-        <v>15252383788.189993</v>
+      <c r="B18" s="3">
+        <v>2909823288.3500142</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3712346352.1500096</v>
+      </c>
+      <c r="D18" s="3">
+        <v>4217305361.4300003</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4412908786.2600002</v>
+      </c>
+      <c r="F18" s="3">
+        <v>15252383788.190022</v>
       </c>
     </row>
   </sheetData>
@@ -948,9 +2954,475 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B81897B5-D195-4B16-A901-6F4970A0D2BD}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2909823288.3499908</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>3712346352.1499872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3">
+        <v>4217305361.4300017</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4412908786.2599974</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3">
+        <v>15252383788.189775</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6310F0B-0B6B-41FD-AFCE-E5A88C9555B9}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s" vm="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>663044066.47000504</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>951745903.30000448</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1295033318.5800047</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1226789622.4600058</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1210946390.6900024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1274610339.0000014</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1173567470.9300017</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1343111582.6100006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1700626307.889998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1641003033.2400024</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1408510868.5399995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1363394884.4799986</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="3">
+        <v>15252383788.189775</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55423D97-67C8-42EB-974A-5247F820D94A}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>663044066.47000504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>951745903.30000448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1295033318.5800047</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3">
+        <v>3712346352.1499872</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3">
+        <v>4217305361.4300017</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3">
+        <v>4412908786.2599974</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3">
+        <v>15252383788.189775</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FEA74E-FE10-421F-9ED5-99978D8842F2}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s" vm="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s" vm="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3">
+        <v>527074.61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3">
+        <v>444909</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3">
+        <v>704330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3">
+        <v>255816</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3">
+        <v>778107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3">
+        <v>166991</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3">
+        <v>415701</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3">
+        <v>262922</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3">
+        <v>337535</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="3">
+        <v>440572</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3">
+        <v>448880</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="3">
+        <v>4782837.6099999994</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>